--- a/chromite_input_template.xlsx
+++ b/chromite_input_template.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chr_python\website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDCE7389-2CED-4CDF-8FE9-5A1F23A28522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB14B66-4C8B-46F4-AE48-5C90C47AADBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="45960" yWindow="7890" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INSTRUCTIONS" sheetId="2" r:id="rId1"/>
-    <sheet name="Input" sheetId="1" r:id="rId2"/>
+    <sheet name="INPUT" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -134,7 +134,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> this sheet before uploading the input file.</t>
+      <t xml:space="preserve"> this sheet before uploading the INPUT file.</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
